--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH87"/>
+  <dimension ref="A1:BH90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="G2" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="H2" t="n">
         <v>3.75</v>
@@ -769,10 +769,10 @@
         <v>3.85</v>
       </c>
       <c r="J2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K2" t="n">
         <v>4.5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -781,22 +781,22 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>7.8</v>
+        <v>1.11</v>
       </c>
       <c r="O2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P2" t="n">
-        <v>3.3</v>
+        <v>1.98</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R2" t="n">
         <v>1.98</v>
       </c>
       <c r="S2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="T2" t="n">
         <v>1.43</v>
@@ -808,7 +808,7 @@
         <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
         <v>42</v>
@@ -847,7 +847,7 @@
         <v>32</v>
       </c>
       <c r="AJ2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK2" t="n">
         <v>19</v>
@@ -871,10 +871,10 @@
         <v>25</v>
       </c>
       <c r="AR2" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT2" t="n">
         <v>17</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -1151,10 +1151,10 @@
         <v>2.32</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="J4" t="n">
         <v>3.9</v>
@@ -1181,10 +1181,10 @@
         <v>1.45</v>
       </c>
       <c r="R4" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T4" t="n">
         <v>1.46</v>
@@ -1193,7 +1193,7 @@
         <v>2.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
         <v>1.75</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -1339,28 +1339,28 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="I5" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="J5" t="n">
         <v>4.6</v>
       </c>
       <c r="K5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
         <v>4.6</v>
@@ -1372,7 +1372,7 @@
         <v>2.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R5" t="n">
         <v>1.49</v>
@@ -1381,19 +1381,19 @@
         <v>2.74</v>
       </c>
       <c r="T5" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="U5" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y5" t="n">
         <v>11</v>
@@ -1408,7 +1408,7 @@
         <v>32</v>
       </c>
       <c r="AC5" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD5" t="n">
         <v>12</v>
@@ -1417,31 +1417,31 @@
         <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AG5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AH5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ5" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AK5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM5" t="n">
         <v>130</v>
       </c>
-      <c r="AL5" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM5" t="n">
+      <c r="AN5" t="n">
         <v>140</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>160</v>
       </c>
       <c r="AO5" t="n">
         <v>7.6</v>
@@ -1453,7 +1453,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS5" t="n">
         <v>10</v>
@@ -1471,38 +1471,38 @@
         <v>11.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AZ5" t="n">
         <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
         <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="T7" t="n">
         <v>1.95</v>
@@ -1823,7 +1823,7 @@
         <v>16.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AQ7" t="n">
         <v>6.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT7" t="n">
         <v>4.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AV7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AY7" t="n">
         <v>4.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB7" t="n">
         <v>4.9</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BD7" t="n">
         <v>6.6</v>
       </c>
       <c r="BE7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG7" t="n">
         <v>7.6</v>
       </c>
-      <c r="BF7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -1945,13 +1945,13 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="O8" t="n">
         <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
         <v>1.18</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>2.86</v>
       </c>
       <c r="K9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2148,13 +2148,13 @@
         <v>1.81</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="T9" t="n">
         <v>1.58</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="O11" t="n">
         <v>1.4</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O13" t="n">
         <v>1.24</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -3091,13 +3091,13 @@
         <v>1.5</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I14" t="n">
         <v>12</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
         <v>5.1</v>
@@ -3118,13 +3118,13 @@
         <v>1.84</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="R14" t="n">
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
         <v>2.22</v>
@@ -3288,7 +3288,7 @@
         <v>3.45</v>
       </c>
       <c r="I15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
         <v>3.7</v>
@@ -3315,10 +3315,10 @@
         <v>1.69</v>
       </c>
       <c r="R15" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="T15" t="n">
         <v>1.62</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3572,7 @@
         <v>46</v>
       </c>
       <c r="AM16" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN16" t="n">
         <v>24</v>
@@ -3602,7 +3602,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AX16" t="n">
         <v>12.5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -3667,46 +3667,46 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="G17" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="H17" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="I17" t="n">
-        <v>140</v>
+        <v>6.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>8.4</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>2.28</v>
+        <v>1.89</v>
       </c>
       <c r="O17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.28</v>
+        <v>1.89</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -3715,10 +3715,10 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="W17" t="n">
-        <v>2.46</v>
+        <v>2.1</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
         <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O18" t="n">
         <v>1.12</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -4061,10 +4061,10 @@
         <v>5.5</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="I19" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="J19" t="n">
         <v>4.3</v>
@@ -4103,7 +4103,7 @@
         <v>2.12</v>
       </c>
       <c r="V19" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="W19" t="n">
         <v>1.22</v>
@@ -4160,7 +4160,7 @@
         <v>75</v>
       </c>
       <c r="AO19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AP19" t="n">
         <v>16</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -4285,10 +4285,10 @@
         <v>1.47</v>
       </c>
       <c r="R20" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="S20" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T20" t="n">
         <v>1.6</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="G22" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="H22" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="I22" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="J22" t="n">
         <v>2.78</v>
       </c>
       <c r="K22" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4679,16 +4679,16 @@
         <v>5.7</v>
       </c>
       <c r="T22" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U22" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="V22" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W22" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="G23" t="n">
         <v>2.66</v>
       </c>
       <c r="H23" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I23" t="n">
         <v>5</v>
@@ -4846,19 +4846,19 @@
         <v>2.82</v>
       </c>
       <c r="K23" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="L23" t="n">
         <v>1.48</v>
       </c>
       <c r="M23" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
         <v>1.37</v>
       </c>
       <c r="O23" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="P23" t="n">
         <v>1.37</v>
@@ -4867,10 +4867,10 @@
         <v>2.46</v>
       </c>
       <c r="R23" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="G24" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H24" t="n">
         <v>4.3</v>
@@ -5037,10 +5037,10 @@
         <v>7.2</v>
       </c>
       <c r="J24" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="K24" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5049,7 +5049,7 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="O24" t="n">
         <v>1.5</v>
@@ -5058,13 +5058,13 @@
         <v>1.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R24" t="n">
         <v>1.12</v>
       </c>
       <c r="S24" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
@@ -5076,7 +5076,7 @@
         <v>1.16</v>
       </c>
       <c r="W24" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -5434,10 +5434,10 @@
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N26" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O26" t="n">
         <v>1.31</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
         <v>11</v>
       </c>
       <c r="I27" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J27" t="n">
         <v>6</v>
@@ -5649,10 +5649,10 @@
         <v>2.38</v>
       </c>
       <c r="T27" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="U27" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V27" t="n">
         <v>1.08</v>
@@ -5709,10 +5709,10 @@
         <v>150</v>
       </c>
       <c r="AN27" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="AO27" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AP27" t="n">
         <v>21</v>
@@ -5721,10 +5721,10 @@
         <v>36</v>
       </c>
       <c r="AR27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS27" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT27" t="n">
         <v>8.6</v>
@@ -5736,7 +5736,7 @@
         <v>34</v>
       </c>
       <c r="AW27" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AX27" t="n">
         <v>7.4</v>
@@ -5748,7 +5748,7 @@
         <v>24</v>
       </c>
       <c r="BA27" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB27" t="n">
         <v>9.4</v>
@@ -5760,17 +5760,17 @@
         <v>27</v>
       </c>
       <c r="BE27" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF27" t="n">
         <v>4.1</v>
       </c>
       <c r="BG27" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -5819,7 +5819,7 @@
         <v>3.85</v>
       </c>
       <c r="L28" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
         <v>1.07</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
         <v>3.55</v>
       </c>
       <c r="L29" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
         <v>1.08</v>
@@ -6049,7 +6049,7 @@
         <v>1.42</v>
       </c>
       <c r="X29" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
         <v>12.5</v>
@@ -6070,7 +6070,7 @@
         <v>16</v>
       </c>
       <c r="AE29" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF29" t="n">
         <v>30</v>
@@ -6091,7 +6091,7 @@
         <v>55</v>
       </c>
       <c r="AL29" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM29" t="n">
         <v>1000</v>
@@ -6103,7 +6103,7 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AQ29" t="n">
         <v>8.199999999999999</v>
@@ -6115,25 +6115,25 @@
         <v>26</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="AU29" t="n">
-        <v>2.24</v>
+        <v>1.97</v>
       </c>
       <c r="AV29" t="n">
         <v>9.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX29" t="n">
         <v>16</v>
       </c>
       <c r="AY29" t="n">
-        <v>2.52</v>
+        <v>2.18</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="BA29" t="n">
         <v>32</v>
@@ -6148,17 +6148,17 @@
         <v>34</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.9</v>
+        <v>2.46</v>
       </c>
       <c r="BF29" t="n">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
         <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N30" t="n">
         <v>2.4</v>
@@ -6225,10 +6225,10 @@
         <v>1.6</v>
       </c>
       <c r="R30" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="S30" t="n">
-        <v>1.62</v>
+        <v>1.02</v>
       </c>
       <c r="T30" t="n">
         <v>1.01</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -6383,19 +6383,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G31" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="H31" t="n">
         <v>4.5</v>
       </c>
       <c r="I31" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J31" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="K31" t="n">
         <v>8</v>
@@ -6404,7 +6404,7 @@
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
         <v>1.73</v>
@@ -6434,7 +6434,7 @@
         <v>1.14</v>
       </c>
       <c r="W31" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6604,7 @@
         <v>2.16</v>
       </c>
       <c r="O32" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P32" t="n">
         <v>2.16</v>
@@ -6613,7 +6613,7 @@
         <v>1.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S32" t="n">
         <v>2.74</v>
@@ -6709,13 +6709,13 @@
         <v>2.2</v>
       </c>
       <c r="AX32" t="n">
-        <v>2.06</v>
+        <v>10</v>
       </c>
       <c r="AY32" t="n">
         <v>2</v>
       </c>
       <c r="AZ32" t="n">
-        <v>11.5</v>
+        <v>2.08</v>
       </c>
       <c r="BA32" t="n">
         <v>2.22</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
         <v>3.15</v>
       </c>
       <c r="K33" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
@@ -6795,10 +6795,10 @@
         <v>1.08</v>
       </c>
       <c r="N33" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="O33" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P33" t="n">
         <v>1.7</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -6986,7 +6986,7 @@
         <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N34" t="n">
         <v>2.4</v>
@@ -7004,7 +7004,7 @@
         <v>1.25</v>
       </c>
       <c r="S34" t="n">
-        <v>2.48</v>
+        <v>1.02</v>
       </c>
       <c r="T34" t="n">
         <v>1.01</v>
@@ -7016,7 +7016,7 @@
         <v>1.58</v>
       </c>
       <c r="W34" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G35" t="n">
         <v>2.92</v>
@@ -7195,10 +7195,10 @@
         <v>1.6</v>
       </c>
       <c r="R35" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="S35" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="T35" t="n">
         <v>1.55</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G36" t="n">
         <v>5</v>
@@ -7377,7 +7377,7 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O36" t="n">
         <v>1.37</v>
@@ -7516,14 +7516,14 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7538,186 +7538,186 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Arges Pitesti</t>
+          <t>KA Akureyri</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Vikingur Reykjavik</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
       </c>
       <c r="M37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O37" t="n">
         <v>1.11</v>
       </c>
-      <c r="N37" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.55</v>
-      </c>
       <c r="P37" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.66</v>
+        <v>1.11</v>
       </c>
       <c r="R37" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S37" t="n">
-        <v>4.8</v>
+        <v>1.11</v>
       </c>
       <c r="T37" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="U37" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="X37" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y37" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Z37" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA37" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC37" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD37" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE37" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG37" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH37" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI37" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK37" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL37" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AO37" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="AQ37" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AR37" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AS37" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="AT37" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU37" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AV37" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW37" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX37" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AY37" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ37" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA37" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BB37" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BC37" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE37" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF37" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7732,55 +7732,55 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KA Akureyri</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
       </c>
       <c r="M38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O38" t="n">
         <v>1.02</v>
       </c>
-      <c r="N38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.11</v>
-      </c>
       <c r="P38" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="R38" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S38" t="n">
-        <v>1.11</v>
+        <v>3.75</v>
       </c>
       <c r="T38" t="n">
         <v>1.01</v>
@@ -7789,10 +7789,10 @@
         <v>1.01</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="W38" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -7935,16 +7935,16 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="G39" t="n">
         <v>4.2</v>
       </c>
       <c r="H39" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="I39" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="J39" t="n">
         <v>3.3</v>
@@ -7959,13 +7959,13 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="O39" t="n">
         <v>1.4</v>
       </c>
       <c r="P39" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="Q39" t="n">
         <v>2.24</v>
@@ -7983,7 +7983,7 @@
         <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W39" t="n">
         <v>1.31</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G40" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H40" t="n">
         <v>3.75</v>
@@ -8141,7 +8141,7 @@
         <v>5.1</v>
       </c>
       <c r="J40" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K40" t="n">
         <v>3.75</v>
@@ -8153,7 +8153,7 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="O40" t="n">
         <v>1.35</v>
@@ -8292,14 +8292,14 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8314,179 +8314,179 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Arges Pitesti</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G41" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="H41" t="n">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="I41" t="n">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="J41" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="K41" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N41" t="n">
-        <v>1.66</v>
+        <v>2.54</v>
       </c>
       <c r="O41" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="P41" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.24</v>
+        <v>2.66</v>
       </c>
       <c r="R41" t="n">
         <v>1.18</v>
       </c>
       <c r="S41" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="T41" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="U41" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="V41" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="W41" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="X41" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y41" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z41" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA41" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB41" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC41" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE41" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF41" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG41" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH41" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI41" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK41" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL41" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM41" t="n">
         <v>1000</v>
       </c>
       <c r="AN41" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO41" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG41" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
         <v>2.96</v>
       </c>
       <c r="G42" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="H42" t="n">
         <v>2.48</v>
@@ -8532,7 +8532,7 @@
         <v>2.98</v>
       </c>
       <c r="K42" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L42" t="n">
         <v>1.4</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -8714,16 +8714,16 @@
         <v>2.3</v>
       </c>
       <c r="G43" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H43" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="I43" t="n">
         <v>3.9</v>
       </c>
       <c r="J43" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K43" t="n">
         <v>3.55</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -8896,31 +8896,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury Merogis</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="G44" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="H44" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="I44" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="J44" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K44" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
@@ -8929,22 +8929,22 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="O44" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="P44" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="R44" t="n">
         <v>1.18</v>
       </c>
       <c r="S44" t="n">
-        <v>3.3</v>
+        <v>1.74</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -8953,10 +8953,10 @@
         <v>1.01</v>
       </c>
       <c r="V44" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="W44" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -9068,14 +9068,14 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9090,67 +9090,67 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Fleury Merogis</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>SV Ried</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.94</v>
+        <v>2.78</v>
       </c>
       <c r="G45" t="n">
-        <v>2.26</v>
+        <v>3.5</v>
       </c>
       <c r="H45" t="n">
-        <v>3.35</v>
+        <v>2.74</v>
       </c>
       <c r="I45" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K45" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="L45" t="n">
         <v>1.01</v>
       </c>
       <c r="M45" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N45" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="O45" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="P45" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.74</v>
+        <v>2.24</v>
       </c>
       <c r="R45" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S45" t="n">
-        <v>1.74</v>
+        <v>3.6</v>
       </c>
       <c r="T45" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U45" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="V45" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="W45" t="n">
-        <v>1.79</v>
+        <v>1.47</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
@@ -9207,52 +9207,52 @@
         <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF45" t="n">
         <v>1.01</v>
@@ -9262,14 +9262,14 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9284,67 +9284,67 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.78</v>
+        <v>2.18</v>
       </c>
       <c r="G46" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="H46" t="n">
-        <v>2.74</v>
+        <v>2.94</v>
       </c>
       <c r="I46" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="J46" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K46" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="L46" t="n">
         <v>1.01</v>
       </c>
       <c r="M46" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="O46" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="P46" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.24</v>
+        <v>1.97</v>
       </c>
       <c r="R46" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S46" t="n">
-        <v>3.6</v>
+        <v>1.97</v>
       </c>
       <c r="T46" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="U46" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="V46" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="W46" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="X46" t="n">
         <v>1000</v>
@@ -9401,52 +9401,52 @@
         <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF46" t="n">
         <v>1.01</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -9487,13 +9487,13 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="G47" t="n">
         <v>2.04</v>
       </c>
       <c r="H47" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I47" t="n">
         <v>7.6</v>
@@ -9650,14 +9650,14 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Hungarian NB I</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9672,55 +9672,55 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ujpest</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nyiregyhaza</t>
+          <t>IA Akranes</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
       </c>
       <c r="M48" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N48" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="O48" t="n">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="P48" t="n">
-        <v>1.97</v>
+        <v>1.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.91</v>
+        <v>1.09</v>
       </c>
       <c r="R48" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="S48" t="n">
-        <v>2.84</v>
+        <v>1.09</v>
       </c>
       <c r="T48" t="n">
         <v>1.01</v>
@@ -9729,10 +9729,10 @@
         <v>1.01</v>
       </c>
       <c r="V48" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="W48" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -9844,14 +9844,14 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Hungarian NB I</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Ujpest</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nyiregyhaza</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.79</v>
+        <v>2.28</v>
       </c>
       <c r="G49" t="n">
-        <v>1.86</v>
+        <v>2.64</v>
       </c>
       <c r="H49" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="J49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K49" t="n">
         <v>3.85</v>
       </c>
-      <c r="K49" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L49" t="n">
         <v>1.01</v>
       </c>
@@ -9899,79 +9899,79 @@
         <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>1.02</v>
+        <v>1.94</v>
       </c>
       <c r="O49" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="P49" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="Q49" t="n">
         <v>1.9</v>
       </c>
       <c r="R49" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S49" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="T49" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="U49" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="V49" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="W49" t="n">
-        <v>2.16</v>
+        <v>1.61</v>
       </c>
       <c r="X49" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y49" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Z49" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA49" t="n">
         <v>1000</v>
       </c>
       <c r="AB49" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC49" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD49" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AE49" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF49" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG49" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH49" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI49" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ49" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK49" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL49" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM49" t="n">
         <v>1000</v>
@@ -9983,62 +9983,62 @@
         <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>2.02</v>
+        <v>1.03</v>
       </c>
       <c r="AQ49" t="n">
-        <v>2.04</v>
+        <v>1.03</v>
       </c>
       <c r="AR49" t="n">
-        <v>2.12</v>
+        <v>1.03</v>
       </c>
       <c r="AS49" t="n">
-        <v>2.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT49" t="n">
-        <v>1.9</v>
+        <v>1.03</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.89</v>
+        <v>1.03</v>
       </c>
       <c r="AV49" t="n">
-        <v>2.06</v>
+        <v>1.03</v>
       </c>
       <c r="AW49" t="n">
-        <v>2.16</v>
+        <v>1.03</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.96</v>
+        <v>1.03</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.93</v>
+        <v>1.03</v>
       </c>
       <c r="AZ49" t="n">
-        <v>2.06</v>
+        <v>1.03</v>
       </c>
       <c r="BA49" t="n">
-        <v>2.16</v>
+        <v>1.03</v>
       </c>
       <c r="BB49" t="n">
-        <v>2.04</v>
+        <v>1.03</v>
       </c>
       <c r="BC49" t="n">
-        <v>2.04</v>
+        <v>1.03</v>
       </c>
       <c r="BD49" t="n">
-        <v>2.12</v>
+        <v>1.03</v>
       </c>
       <c r="BE49" t="n">
-        <v>2.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF49" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG49" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -10060,49 +10060,49 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Grenoble</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>1.79</v>
       </c>
       <c r="G50" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="H50" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I50" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="J50" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="K50" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L50" t="n">
         <v>1.01</v>
       </c>
       <c r="M50" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N50" t="n">
-        <v>3.85</v>
+        <v>1.02</v>
       </c>
       <c r="O50" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="P50" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="R50" t="n">
         <v>1.33</v>
@@ -10111,128 +10111,128 @@
         <v>2.78</v>
       </c>
       <c r="T50" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="U50" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="V50" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W50" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="X50" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y50" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Z50" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AA50" t="n">
         <v>1000</v>
       </c>
       <c r="AB50" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC50" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD50" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AE50" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AF50" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AG50" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH50" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AI50" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AJ50" t="n">
         <v>28</v>
       </c>
       <c r="AK50" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL50" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM50" t="n">
         <v>1000</v>
       </c>
       <c r="AN50" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO50" t="n">
         <v>1000</v>
       </c>
       <c r="AP50" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AX50" t="n">
         <v>2.28</v>
       </c>
-      <c r="AQ50" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>1.99</v>
-      </c>
       <c r="AY50" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="AZ50" t="n">
-        <v>15</v>
+        <v>2.42</v>
       </c>
       <c r="BA50" t="n">
-        <v>44</v>
+        <v>2.56</v>
       </c>
       <c r="BB50" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="BC50" t="n">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="BD50" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="BE50" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="BF50" t="n">
-        <v>2.28</v>
+        <v>6.8</v>
       </c>
       <c r="BG50" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -10254,179 +10254,179 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Grenoble</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.98</v>
+        <v>1.79</v>
       </c>
       <c r="G51" t="n">
-        <v>3.3</v>
+        <v>1.92</v>
       </c>
       <c r="H51" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I51" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J51" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P51" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W51" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX51" t="n">
         <v>2.32</v>
       </c>
-      <c r="I51" t="n">
+      <c r="AY51" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB51" t="n">
         <v>2.48</v>
       </c>
-      <c r="J51" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K51" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M51" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N51" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O51" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P51" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T51" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U51" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X51" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD51" t="n">
+      <c r="BC51" t="n">
         <v>12.5</v>
       </c>
-      <c r="AE51" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>17</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>7</v>
-      </c>
       <c r="BD51" t="n">
-        <v>7.2</v>
+        <v>2.56</v>
       </c>
       <c r="BE51" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BF51" t="n">
         <v>7.8</v>
       </c>
-      <c r="BF51" t="n">
-        <v>18</v>
-      </c>
       <c r="BG51" t="n">
-        <v>11.5</v>
+        <v>2.68</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -10448,179 +10448,179 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Amiens</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.83</v>
+        <v>2.98</v>
       </c>
       <c r="G52" t="n">
-        <v>1.95</v>
+        <v>3.3</v>
       </c>
       <c r="H52" t="n">
-        <v>4.2</v>
+        <v>2.32</v>
       </c>
       <c r="I52" t="n">
-        <v>4.7</v>
+        <v>2.48</v>
       </c>
       <c r="J52" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="K52" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N52" t="n">
         <v>4.3</v>
       </c>
-      <c r="L52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N52" t="n">
-        <v>2.14</v>
-      </c>
       <c r="O52" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P52" t="n">
         <v>2.14</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R52" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S52" t="n">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="T52" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="U52" t="n">
-        <v>1.84</v>
+        <v>2.28</v>
       </c>
       <c r="V52" t="n">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="W52" t="n">
-        <v>2.04</v>
+        <v>1.43</v>
       </c>
       <c r="X52" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF52" t="n">
         <v>24</v>
       </c>
-      <c r="Y52" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB52" t="n">
+      <c r="AG52" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC52" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE52" t="n">
+      <c r="AH52" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM52" t="n">
         <v>75</v>
       </c>
-      <c r="AF52" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK52" t="n">
+      <c r="AN52" t="n">
         <v>27</v>
       </c>
-      <c r="AL52" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN52" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO52" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.14</v>
+        <v>16</v>
       </c>
       <c r="AQ52" t="n">
-        <v>2.14</v>
+        <v>10.5</v>
       </c>
       <c r="AR52" t="n">
-        <v>2.24</v>
+        <v>14</v>
       </c>
       <c r="AS52" t="n">
-        <v>2.34</v>
+        <v>7</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.02</v>
+        <v>12</v>
       </c>
       <c r="AU52" t="n">
-        <v>1.98</v>
+        <v>7.2</v>
       </c>
       <c r="AV52" t="n">
-        <v>2.14</v>
+        <v>10</v>
       </c>
       <c r="AW52" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="AX52" t="n">
-        <v>2.06</v>
+        <v>19</v>
       </c>
       <c r="AY52" t="n">
-        <v>2.02</v>
+        <v>11.5</v>
       </c>
       <c r="AZ52" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>32</v>
+        <v>7.2</v>
       </c>
       <c r="BB52" t="n">
-        <v>2.18</v>
+        <v>7.6</v>
       </c>
       <c r="BC52" t="n">
-        <v>2.16</v>
+        <v>7</v>
       </c>
       <c r="BD52" t="n">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="BE52" t="n">
-        <v>2.34</v>
+        <v>7.8</v>
       </c>
       <c r="BF52" t="n">
-        <v>2.34</v>
+        <v>18</v>
       </c>
       <c r="BG52" t="n">
-        <v>2.34</v>
+        <v>11.5</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -10642,186 +10642,186 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Amiens</t>
         </is>
       </c>
       <c r="F53" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H53" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I53" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J53" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K53" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N53" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P53" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W53" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X53" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AR53" t="n">
         <v>2.66</v>
       </c>
-      <c r="G53" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H53" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="I53" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="J53" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K53" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AS53" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="AT53" t="n">
-        <v>7.2</v>
+        <v>2.36</v>
       </c>
       <c r="AU53" t="n">
-        <v>2.94</v>
+        <v>2.3</v>
       </c>
       <c r="AV53" t="n">
-        <v>9.6</v>
+        <v>2.52</v>
       </c>
       <c r="AW53" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="AX53" t="n">
-        <v>13</v>
+        <v>2.42</v>
       </c>
       <c r="AY53" t="n">
-        <v>9.4</v>
+        <v>2.36</v>
       </c>
       <c r="AZ53" t="n">
-        <v>3.7</v>
+        <v>12.5</v>
       </c>
       <c r="BA53" t="n">
-        <v>4.1</v>
+        <v>32</v>
       </c>
       <c r="BB53" t="n">
-        <v>4.1</v>
+        <v>2.56</v>
       </c>
       <c r="BC53" t="n">
-        <v>4</v>
+        <v>2.54</v>
       </c>
       <c r="BD53" t="n">
-        <v>4.1</v>
+        <v>21</v>
       </c>
       <c r="BE53" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="BF53" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="BG53" t="n">
-        <v>4</v>
+        <v>2.78</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -10836,73 +10836,73 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FC Dordrecht</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2</v>
+        <v>2.66</v>
       </c>
       <c r="G54" t="n">
-        <v>2.22</v>
+        <v>3.4</v>
       </c>
       <c r="H54" t="n">
-        <v>3.25</v>
+        <v>2.74</v>
       </c>
       <c r="I54" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="J54" t="n">
-        <v>3.9</v>
+        <v>2.96</v>
       </c>
       <c r="K54" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="L54" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="N54" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.54</v>
+        <v>1.69</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.54</v>
+        <v>2.18</v>
       </c>
       <c r="R54" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U54" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V54" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y54" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z54" t="n">
         <v>1000</v>
@@ -10911,13 +10911,13 @@
         <v>1000</v>
       </c>
       <c r="AB54" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC54" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD54" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE54" t="n">
         <v>1000</v>
@@ -10926,7 +10926,7 @@
         <v>1000</v>
       </c>
       <c r="AG54" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH54" t="n">
         <v>1000</v>
@@ -10953,62 +10953,62 @@
         <v>1000</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AU54" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="AV54" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BA54" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC54" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD54" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG54" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -11030,31 +11030,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>FC Dordrecht</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="G55" t="n">
-        <v>1.88</v>
+        <v>2.22</v>
       </c>
       <c r="H55" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="I55" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="J55" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="K55" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L55" t="n">
         <v>1.01</v>
@@ -11063,153 +11063,153 @@
         <v>1.03</v>
       </c>
       <c r="N55" t="n">
-        <v>4.9</v>
+        <v>2.56</v>
       </c>
       <c r="O55" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P55" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="Q55" t="n">
         <v>1.53</v>
       </c>
       <c r="R55" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="S55" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="T55" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="U55" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="V55" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="W55" t="n">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="X55" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Y55" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z55" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA55" t="n">
         <v>1000</v>
       </c>
       <c r="AB55" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AC55" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AD55" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE55" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF55" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG55" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH55" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI55" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ55" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK55" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL55" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM55" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN55" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AO55" t="n">
         <v>1000</v>
       </c>
       <c r="AP55" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="AQ55" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="AR55" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="AT55" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="AU55" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV55" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="AW55" t="n">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="AX55" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY55" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ55" t="n">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="BA55" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="BB55" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BC55" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD55" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE55" t="n">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BF55" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG55" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -11224,55 +11224,55 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Jong FC Utrecht</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IA Akranes</t>
+          <t>FC Eindhoven</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L56" t="n">
         <v>1.01</v>
       </c>
       <c r="M56" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N56" t="n">
-        <v>1.25</v>
+        <v>2.72</v>
       </c>
       <c r="O56" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="P56" t="n">
-        <v>1.25</v>
+        <v>2.72</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="R56" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="S56" t="n">
-        <v>1.09</v>
+        <v>2</v>
       </c>
       <c r="T56" t="n">
         <v>1.01</v>
@@ -11281,10 +11281,10 @@
         <v>1.01</v>
       </c>
       <c r="V56" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="W56" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="X56" t="n">
         <v>1000</v>
@@ -11341,52 +11341,52 @@
         <v>1000</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF56" t="n">
         <v>1.01</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -11460,13 +11460,13 @@
         <v>2.92</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R57" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="S57" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="T57" t="n">
         <v>1.54</v>
@@ -11514,7 +11514,7 @@
         <v>22</v>
       </c>
       <c r="AI57" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ57" t="n">
         <v>25</v>
@@ -11526,16 +11526,16 @@
         <v>30</v>
       </c>
       <c r="AM57" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN57" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO57" t="n">
         <v>1000</v>
       </c>
       <c r="AP57" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="AQ57" t="n">
         <v>21</v>
@@ -11544,7 +11544,7 @@
         <v>30</v>
       </c>
       <c r="AS57" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="AT57" t="n">
         <v>11</v>
@@ -11556,13 +11556,13 @@
         <v>14.5</v>
       </c>
       <c r="AW57" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AX57" t="n">
         <v>10</v>
       </c>
       <c r="AY57" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AZ57" t="n">
         <v>11.5</v>
@@ -11571,26 +11571,26 @@
         <v>28</v>
       </c>
       <c r="BB57" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="BC57" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="BD57" t="n">
         <v>17</v>
       </c>
       <c r="BE57" t="n">
-        <v>2.42</v>
+        <v>36</v>
       </c>
       <c r="BF57" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BG57" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -11657,7 +11657,7 @@
         <v>1.3</v>
       </c>
       <c r="R58" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="S58" t="n">
         <v>1.7</v>
@@ -11732,16 +11732,16 @@
         <v>2.58</v>
       </c>
       <c r="AQ58" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AR58" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AS58" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AT58" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AU58" t="n">
         <v>9.800000000000001</v>
@@ -11750,13 +11750,13 @@
         <v>2.34</v>
       </c>
       <c r="AW58" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AX58" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AY58" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AZ58" t="n">
         <v>10</v>
@@ -11774,7 +11774,7 @@
         <v>15</v>
       </c>
       <c r="BE58" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BF58" t="n">
         <v>3.95</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
         <v>2.2</v>
       </c>
       <c r="I59" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="J59" t="n">
         <v>3.85</v>
@@ -11848,7 +11848,7 @@
         <v>2.52</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R59" t="n">
         <v>1.6</v>
@@ -11863,7 +11863,7 @@
         <v>2.58</v>
       </c>
       <c r="V59" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W59" t="n">
         <v>1.45</v>
@@ -11920,65 +11920,65 @@
         <v>1000</v>
       </c>
       <c r="AO59" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.82</v>
+        <v>2.06</v>
       </c>
       <c r="AS59" t="n">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="AT59" t="n">
-        <v>1.82</v>
+        <v>2.06</v>
       </c>
       <c r="AU59" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AV59" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AW59" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="AX59" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AY59" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ59" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="BA59" t="n">
         <v>19.5</v>
       </c>
       <c r="BB59" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="BC59" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="BD59" t="n">
         <v>22</v>
       </c>
       <c r="BE59" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="BF59" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="BG59" t="n">
-        <v>1.96</v>
+        <v>7.8</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -12009,19 +12009,19 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G60" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="H60" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="I60" t="n">
-        <v>2.98</v>
+        <v>3.9</v>
       </c>
       <c r="J60" t="n">
-        <v>3.75</v>
+        <v>2.56</v>
       </c>
       <c r="K60" t="n">
         <v>4.5</v>
@@ -12057,10 +12057,10 @@
         <v>1.01</v>
       </c>
       <c r="V60" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W60" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="X60" t="n">
         <v>1000</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -12203,10 +12203,10 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="G61" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H61" t="n">
         <v>4.7</v>
@@ -12251,7 +12251,7 @@
         <v>1.01</v>
       </c>
       <c r="V61" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W61" t="n">
         <v>2.28</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -12442,7 +12442,7 @@
         <v>1.42</v>
       </c>
       <c r="U62" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V62" t="n">
         <v>1.62</v>
@@ -12505,16 +12505,16 @@
         <v>1000</v>
       </c>
       <c r="AP62" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AQ62" t="n">
         <v>2.16</v>
       </c>
       <c r="AR62" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AS62" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AT62" t="n">
         <v>10.5</v>
@@ -12523,10 +12523,10 @@
         <v>2.04</v>
       </c>
       <c r="AV62" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AW62" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AX62" t="n">
         <v>16</v>
@@ -12538,19 +12538,19 @@
         <v>10.5</v>
       </c>
       <c r="BA62" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BB62" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BC62" t="n">
         <v>19.5</v>
       </c>
       <c r="BD62" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BE62" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BF62" t="n">
         <v>2.44</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -12603,7 +12603,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="J63" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="K63" t="n">
         <v>6.6</v>
@@ -12624,7 +12624,7 @@
         <v>3.1</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R63" t="n">
         <v>1.78</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -12776,31 +12776,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Jong FC Utrecht</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FC Eindhoven</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2.26</v>
+        <v>1.71</v>
       </c>
       <c r="G64" t="n">
-        <v>2.46</v>
+        <v>1.88</v>
       </c>
       <c r="H64" t="n">
-        <v>2.82</v>
+        <v>4.4</v>
       </c>
       <c r="I64" t="n">
-        <v>3.15</v>
+        <v>5.1</v>
       </c>
       <c r="J64" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K64" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="L64" t="n">
         <v>1.01</v>
@@ -12809,146 +12809,146 @@
         <v>1.03</v>
       </c>
       <c r="N64" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P64" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S64" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W64" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="X64" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AR64" t="n">
         <v>2.72</v>
       </c>
-      <c r="O64" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P64" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S64" t="n">
-        <v>2</v>
-      </c>
-      <c r="T64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V64" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W64" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="X64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR64" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AS64" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="AT64" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="AU64" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="AV64" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="AW64" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="AX64" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY64" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="AZ64" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BA64" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BB64" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BC64" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BD64" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BE64" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BF64" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG64" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -12979,7 +12979,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G65" t="n">
         <v>2.64</v>
@@ -13015,10 +13015,10 @@
         <v>1.73</v>
       </c>
       <c r="R65" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S65" t="n">
-        <v>1.73</v>
+        <v>2.76</v>
       </c>
       <c r="T65" t="n">
         <v>1.01</v>
@@ -13087,52 +13087,52 @@
         <v>1000</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF65" t="n">
         <v>1.01</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -13173,22 +13173,22 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="G66" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="H66" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="I66" t="n">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="J66" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="K66" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="L66" t="n">
         <v>1.01</v>
@@ -13221,10 +13221,10 @@
         <v>1.01</v>
       </c>
       <c r="V66" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="W66" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="X66" t="n">
         <v>1000</v>
@@ -13281,52 +13281,52 @@
         <v>1000</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF66" t="n">
         <v>1.01</v>
@@ -13336,14 +13336,14 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -13358,186 +13358,186 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Legia Warsaw</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Zaglebie Lubin</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.65</v>
+        <v>3.1</v>
       </c>
       <c r="G67" t="n">
-        <v>1.79</v>
+        <v>3.35</v>
       </c>
       <c r="H67" t="n">
-        <v>5.5</v>
+        <v>2.22</v>
       </c>
       <c r="I67" t="n">
-        <v>6.6</v>
+        <v>2.36</v>
       </c>
       <c r="J67" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K67" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L67" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M67" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N67" t="n">
-        <v>3.5</v>
+        <v>2.46</v>
       </c>
       <c r="O67" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="P67" t="n">
-        <v>1.87</v>
+        <v>2.46</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.99</v>
+        <v>1.59</v>
       </c>
       <c r="R67" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S67" t="n">
-        <v>3.4</v>
+        <v>2.22</v>
       </c>
       <c r="T67" t="n">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="U67" t="n">
-        <v>1.76</v>
+        <v>2.34</v>
       </c>
       <c r="V67" t="n">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="W67" t="n">
-        <v>2.26</v>
+        <v>1.43</v>
       </c>
       <c r="X67" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="Y67" t="n">
         <v>19.5</v>
       </c>
       <c r="Z67" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="AA67" t="n">
-        <v>210</v>
+        <v>32</v>
       </c>
       <c r="AB67" t="n">
-        <v>9.6</v>
+        <v>21</v>
       </c>
       <c r="AC67" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AD67" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE67" t="n">
         <v>24</v>
       </c>
-      <c r="AE67" t="n">
-        <v>110</v>
-      </c>
       <c r="AF67" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY67" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG67" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH67" t="n">
+      <c r="AZ67" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC67" t="n">
         <v>23</v>
       </c>
-      <c r="AI67" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ67" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK67" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL67" t="n">
+      <c r="BD67" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE67" t="n">
         <v>42</v>
       </c>
-      <c r="AM67" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN67" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO67" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP67" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AQ67" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR67" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS67" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT67" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU67" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV67" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AW67" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX67" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY67" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ67" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BA67" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BB67" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC67" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD67" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE67" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BF67" t="n">
-        <v>8.4</v>
+        <v>4.1</v>
       </c>
       <c r="BG67" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -13552,186 +13552,186 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Legia Warsaw</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AC Monza</t>
+          <t>Zaglebie Lubin</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3.65</v>
+        <v>1.65</v>
       </c>
       <c r="G68" t="n">
-        <v>4.1</v>
+        <v>1.79</v>
       </c>
       <c r="H68" t="n">
-        <v>2.18</v>
+        <v>5.5</v>
       </c>
       <c r="I68" t="n">
-        <v>2.34</v>
+        <v>6.6</v>
       </c>
       <c r="J68" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="K68" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="L68" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M68" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N68" t="n">
-        <v>1.72</v>
+        <v>3.5</v>
       </c>
       <c r="O68" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="P68" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="R68" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="S68" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W68" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="X68" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA68" t="n">
         <v>3.6</v>
       </c>
-      <c r="T68" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U68" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V68" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="W68" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X68" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE68" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG68" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH68" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI68" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ68" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK68" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL68" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP68" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ68" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR68" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS68" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AT68" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU68" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AV68" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW68" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX68" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY68" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ68" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA68" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BB68" t="n">
-        <v>3.15</v>
+        <v>5.5</v>
       </c>
       <c r="BC68" t="n">
-        <v>34</v>
+        <v>5.6</v>
       </c>
       <c r="BD68" t="n">
-        <v>42</v>
+        <v>6.6</v>
       </c>
       <c r="BE68" t="n">
-        <v>3.25</v>
+        <v>7.6</v>
       </c>
       <c r="BF68" t="n">
-        <v>3.25</v>
+        <v>8.4</v>
       </c>
       <c r="BG68" t="n">
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Austrian Erste Liga</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -13746,55 +13746,55 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Sociedad B</t>
+          <t>Admira Wacker</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>First Vienna Fc 1894</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>3.1</v>
+        <v>1.61</v>
       </c>
       <c r="G69" t="n">
+        <v>2</v>
+      </c>
+      <c r="H69" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I69" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J69" t="n">
         <v>3.4</v>
       </c>
-      <c r="H69" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="I69" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J69" t="n">
-        <v>3.9</v>
-      </c>
       <c r="K69" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="L69" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M69" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N69" t="n">
-        <v>2.48</v>
+        <v>1.63</v>
       </c>
       <c r="O69" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="P69" t="n">
-        <v>2.48</v>
+        <v>1.63</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="R69" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S69" t="n">
-        <v>2.22</v>
+        <v>3.3</v>
       </c>
       <c r="T69" t="n">
         <v>1.01</v>
@@ -13803,129 +13803,129 @@
         <v>1.01</v>
       </c>
       <c r="V69" t="n">
-        <v>1.76</v>
+        <v>1.15</v>
       </c>
       <c r="W69" t="n">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="X69" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Y69" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z69" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA69" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB69" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC69" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD69" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE69" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF69" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG69" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH69" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI69" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AJ69" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK69" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL69" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM69" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN69" t="n">
         <v>1000</v>
       </c>
       <c r="AO69" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AP69" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ69" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="AR69" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS69" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AT69" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU69" t="n">
-        <v>3.1</v>
+        <v>1.03</v>
       </c>
       <c r="AV69" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="AW69" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="AX69" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY69" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ69" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BA69" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB69" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BC69" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BD69" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BE69" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BF69" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG69" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Bosnian Premier League</t>
+          <t>German Bundesliga</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -13940,186 +13940,186 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Zeljeznicar</t>
+          <t>St Pauli</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nk Posusje</t>
+          <t>FC Koln</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="G70" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="H70" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="I70" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="J70" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="K70" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L70" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M70" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N70" t="n">
-        <v>1.24</v>
+        <v>3.45</v>
       </c>
       <c r="O70" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="P70" t="n">
-        <v>1.24</v>
+        <v>1.82</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="R70" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S70" t="n">
-        <v>1.02</v>
+        <v>4.1</v>
       </c>
       <c r="T70" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U70" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V70" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="W70" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="X70" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y70" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z70" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA70" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB70" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC70" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD70" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE70" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF70" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG70" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH70" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI70" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ70" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK70" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL70" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM70" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN70" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO70" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR70" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AS70" t="n">
-        <v>1.03</v>
+        <v>40</v>
       </c>
       <c r="AT70" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AU70" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV70" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AW70" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="AX70" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AY70" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AZ70" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BA70" t="n">
-        <v>1.03</v>
+        <v>42</v>
       </c>
       <c r="BB70" t="n">
-        <v>1.03</v>
+        <v>40</v>
       </c>
       <c r="BC70" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BD70" t="n">
-        <v>1.03</v>
+        <v>42</v>
       </c>
       <c r="BE70" t="n">
-        <v>1.03</v>
+        <v>40</v>
       </c>
       <c r="BF70" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG70" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Austrian Erste Liga</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -14134,31 +14134,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Admira Wacker</t>
+          <t>Zeljeznicar</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>First Vienna Fc 1894</t>
+          <t>Nk Posusje</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1.61</v>
+        <v>1.04</v>
       </c>
       <c r="G71" t="n">
-        <v>1.91</v>
+        <v>1000</v>
       </c>
       <c r="H71" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="I71" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="J71" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="K71" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="L71" t="n">
         <v>1.01</v>
@@ -14170,19 +14170,19 @@
         <v>1.25</v>
       </c>
       <c r="O71" t="n">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
       <c r="P71" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.94</v>
+        <v>1.47</v>
       </c>
       <c r="R71" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S71" t="n">
-        <v>3.3</v>
+        <v>1.47</v>
       </c>
       <c r="T71" t="n">
         <v>1.01</v>
@@ -14191,10 +14191,10 @@
         <v>1.01</v>
       </c>
       <c r="V71" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="W71" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="X71" t="n">
         <v>1000</v>
@@ -14306,14 +14306,14 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>German Bundesliga</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -14328,179 +14328,179 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>St Pauli</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FC Koln</t>
+          <t>AC Monza</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2.8</v>
+        <v>3.65</v>
       </c>
       <c r="G72" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="H72" t="n">
-        <v>2.8</v>
+        <v>2.18</v>
       </c>
       <c r="I72" t="n">
-        <v>2.84</v>
+        <v>2.36</v>
       </c>
       <c r="J72" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K72" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L72" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M72" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N72" t="n">
-        <v>3.4</v>
+        <v>1.73</v>
       </c>
       <c r="O72" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P72" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R72" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="T72" t="n">
         <v>1.87</v>
       </c>
       <c r="U72" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="V72" t="n">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="W72" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="X72" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y72" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY72" t="n">
         <v>10.5</v>
-      </c>
-      <c r="Z72" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD72" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE72" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF72" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG72" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH72" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI72" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ72" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK72" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL72" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM72" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN72" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO72" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP72" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ72" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR72" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS72" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT72" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU72" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV72" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW72" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX72" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY72" t="n">
-        <v>11.5</v>
       </c>
       <c r="AZ72" t="n">
         <v>16.5</v>
       </c>
       <c r="BA72" t="n">
-        <v>42</v>
+        <v>3.15</v>
       </c>
       <c r="BB72" t="n">
-        <v>40</v>
+        <v>3.2</v>
       </c>
       <c r="BC72" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BD72" t="n">
         <v>42</v>
       </c>
       <c r="BE72" t="n">
-        <v>40</v>
+        <v>3.3</v>
       </c>
       <c r="BF72" t="n">
-        <v>20</v>
+        <v>3.25</v>
       </c>
       <c r="BG72" t="n">
-        <v>27</v>
+        <v>3.25</v>
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -14531,7 +14531,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="G73" t="n">
         <v>1.24</v>
@@ -14549,28 +14549,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="L73" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="M73" t="n">
         <v>1.03</v>
       </c>
       <c r="N73" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O73" t="n">
         <v>1.2</v>
       </c>
       <c r="P73" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q73" t="n">
         <v>1.61</v>
       </c>
       <c r="R73" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S73" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="T73" t="n">
         <v>2.36</v>
@@ -14585,7 +14585,7 @@
         <v>5.2</v>
       </c>
       <c r="X73" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y73" t="n">
         <v>48</v>
@@ -14597,7 +14597,7 @@
         <v>1000</v>
       </c>
       <c r="AB73" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC73" t="n">
         <v>18</v>
@@ -14606,7 +14606,7 @@
         <v>65</v>
       </c>
       <c r="AE73" t="n">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AF73" t="n">
         <v>7.6</v>
@@ -14624,13 +14624,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AK73" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AL73" t="n">
         <v>50</v>
       </c>
       <c r="AM73" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AN73" t="n">
         <v>4.1</v>
@@ -14639,16 +14639,16 @@
         <v>1000</v>
       </c>
       <c r="AP73" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AQ73" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AR73" t="n">
         <v>44</v>
       </c>
       <c r="AS73" t="n">
-        <v>60</v>
+        <v>15.5</v>
       </c>
       <c r="AT73" t="n">
         <v>8.199999999999999</v>
@@ -14669,7 +14669,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ73" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BA73" t="n">
         <v>48</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -14731,19 +14731,19 @@
         <v>7.4</v>
       </c>
       <c r="H74" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="I74" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="J74" t="n">
-        <v>3.3</v>
+        <v>1.09</v>
       </c>
       <c r="K74" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="L74" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M74" t="n">
         <v>1.01</v>
@@ -14758,7 +14758,7 @@
         <v>1.58</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="R74" t="n">
         <v>1.2</v>
@@ -14773,10 +14773,10 @@
         <v>1.01</v>
       </c>
       <c r="V74" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W74" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X74" t="n">
         <v>1000</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -14910,55 +14910,55 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>2.26</v>
+        <v>1.88</v>
       </c>
       <c r="G75" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="H75" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="I75" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K75" t="n">
         <v>3.9</v>
       </c>
-      <c r="J75" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K75" t="n">
-        <v>3.5</v>
-      </c>
       <c r="L75" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M75" t="n">
         <v>1.01</v>
       </c>
       <c r="N75" t="n">
-        <v>3.1</v>
+        <v>1.89</v>
       </c>
       <c r="O75" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="P75" t="n">
-        <v>1.73</v>
+        <v>1.28</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="R75" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S75" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="T75" t="n">
         <v>1.01</v>
@@ -14967,55 +14967,55 @@
         <v>1.01</v>
       </c>
       <c r="V75" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="W75" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X75" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y75" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z75" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA75" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB75" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC75" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD75" t="n">
         <v>1000</v>
       </c>
       <c r="AE75" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF75" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG75" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH75" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI75" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ75" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK75" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL75" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM75" t="n">
         <v>1000</v>
@@ -15027,69 +15027,69 @@
         <v>1000</v>
       </c>
       <c r="AP75" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ75" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR75" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS75" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT75" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="AU75" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV75" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="AW75" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AX75" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY75" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ75" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="BA75" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB75" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="BC75" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD75" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="BE75" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BF75" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BG75" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -15104,70 +15104,70 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>Longford</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="G76" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="H76" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="I76" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="J76" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="K76" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L76" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M76" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N76" t="n">
-        <v>1.89</v>
+        <v>3.8</v>
       </c>
       <c r="O76" t="n">
         <v>1.3</v>
       </c>
       <c r="P76" t="n">
-        <v>1.28</v>
+        <v>1.92</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="R76" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S76" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="T76" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U76" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V76" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="W76" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="X76" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y76" t="n">
         <v>1000</v>
@@ -15179,10 +15179,10 @@
         <v>1000</v>
       </c>
       <c r="AB76" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC76" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD76" t="n">
         <v>1000</v>
@@ -15191,10 +15191,10 @@
         <v>1000</v>
       </c>
       <c r="AF76" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG76" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH76" t="n">
         <v>1000</v>
@@ -15215,75 +15215,75 @@
         <v>1000</v>
       </c>
       <c r="AN76" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO76" t="n">
         <v>1000</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR76" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS76" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT76" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU76" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV76" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW76" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX76" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY76" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ76" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA76" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB76" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BC76" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BD76" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE76" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF76" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG76" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -15298,179 +15298,179 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Longford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1.84</v>
+        <v>2.26</v>
       </c>
       <c r="G77" t="n">
-        <v>2.08</v>
+        <v>2.44</v>
       </c>
       <c r="H77" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="I77" t="n">
-        <v>5.6</v>
+        <v>3.9</v>
       </c>
       <c r="J77" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K77" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="L77" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M77" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N77" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="O77" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="P77" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.74</v>
+        <v>2.22</v>
       </c>
       <c r="R77" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="S77" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="T77" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="U77" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="V77" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="W77" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="X77" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="Y77" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z77" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA77" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB77" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC77" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD77" t="n">
         <v>1000</v>
       </c>
       <c r="AE77" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF77" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AG77" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH77" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI77" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ77" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK77" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL77" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM77" t="n">
         <v>1000</v>
       </c>
       <c r="AN77" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AO77" t="n">
         <v>1000</v>
       </c>
       <c r="AP77" t="n">
-        <v>11</v>
+        <v>2.22</v>
       </c>
       <c r="AQ77" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AR77" t="n">
-        <v>3.9</v>
+        <v>16.5</v>
       </c>
       <c r="AS77" t="n">
-        <v>4.1</v>
+        <v>2.54</v>
       </c>
       <c r="AT77" t="n">
-        <v>6.8</v>
+        <v>2.1</v>
       </c>
       <c r="AU77" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AV77" t="n">
-        <v>13</v>
+        <v>2.6</v>
       </c>
       <c r="AW77" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="AX77" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY77" t="n">
-        <v>7.6</v>
+        <v>2.22</v>
       </c>
       <c r="AZ77" t="n">
-        <v>13.5</v>
+        <v>2.36</v>
       </c>
       <c r="BA77" t="n">
-        <v>4</v>
+        <v>2.52</v>
       </c>
       <c r="BB77" t="n">
-        <v>15.5</v>
+        <v>2.46</v>
       </c>
       <c r="BC77" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="BD77" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="BE77" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="BF77" t="n">
-        <v>9.4</v>
+        <v>2.6</v>
       </c>
       <c r="BG77" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -15504,7 +15504,7 @@
         <v>1.28</v>
       </c>
       <c r="G78" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="H78" t="n">
         <v>8</v>
@@ -15534,13 +15534,13 @@
         <v>1.9</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="R78" t="n">
         <v>1.21</v>
       </c>
       <c r="S78" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="T78" t="n">
         <v>1.01</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -15698,16 +15698,16 @@
         <v>1.92</v>
       </c>
       <c r="G79" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="H79" t="n">
         <v>3.4</v>
       </c>
       <c r="I79" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J79" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K79" t="n">
         <v>5.3</v>
@@ -15743,10 +15743,10 @@
         <v>2.08</v>
       </c>
       <c r="V79" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W79" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="X79" t="n">
         <v>1000</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -15889,13 +15889,13 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G80" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="H80" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="I80" t="n">
         <v>4</v>
@@ -15904,7 +15904,7 @@
         <v>2.78</v>
       </c>
       <c r="K80" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L80" t="n">
         <v>1.35</v>
@@ -15925,7 +15925,7 @@
         <v>1.98</v>
       </c>
       <c r="R80" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="S80" t="n">
         <v>3.5</v>
@@ -15940,7 +15940,7 @@
         <v>1.33</v>
       </c>
       <c r="W80" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="X80" t="n">
         <v>1000</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -16083,7 +16083,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G81" t="n">
         <v>1.61</v>
@@ -16101,7 +16101,7 @@
         <v>4.7</v>
       </c>
       <c r="L81" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M81" t="n">
         <v>1.05</v>
@@ -16137,13 +16137,13 @@
         <v>2.62</v>
       </c>
       <c r="X81" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y81" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z81" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AA81" t="n">
         <v>200</v>
@@ -16170,7 +16170,7 @@
         <v>21</v>
       </c>
       <c r="AI81" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AJ81" t="n">
         <v>15.5</v>
@@ -16185,7 +16185,7 @@
         <v>120</v>
       </c>
       <c r="AN81" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO81" t="n">
         <v>110</v>
@@ -16200,10 +16200,10 @@
         <v>36</v>
       </c>
       <c r="AS81" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT81" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU81" t="n">
         <v>9.199999999999999</v>
@@ -16212,7 +16212,7 @@
         <v>21</v>
       </c>
       <c r="AW81" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX81" t="n">
         <v>9.199999999999999</v>
@@ -16224,7 +16224,7 @@
         <v>17.5</v>
       </c>
       <c r="BA81" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB81" t="n">
         <v>13</v>
@@ -16233,20 +16233,20 @@
         <v>14</v>
       </c>
       <c r="BD81" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BE81" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF81" t="n">
         <v>6.8</v>
       </c>
       <c r="BG81" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -16277,7 +16277,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G82" t="n">
         <v>3.95</v>
@@ -16292,7 +16292,7 @@
         <v>3.2</v>
       </c>
       <c r="K82" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L82" t="n">
         <v>1.3</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -16471,13 +16471,13 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G83" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="H83" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I83" t="n">
         <v>3.95</v>
@@ -16486,10 +16486,10 @@
         <v>3.15</v>
       </c>
       <c r="K83" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="L83" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M83" t="n">
         <v>1.01</v>
@@ -16513,7 +16513,7 @@
         <v>3.85</v>
       </c>
       <c r="T83" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U83" t="n">
         <v>1.01</v>
@@ -16522,13 +16522,13 @@
         <v>1.34</v>
       </c>
       <c r="W83" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="X83" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y83" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z83" t="n">
         <v>34</v>
@@ -16552,7 +16552,7 @@
         <v>21</v>
       </c>
       <c r="AG83" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH83" t="n">
         <v>29</v>
@@ -16564,7 +16564,7 @@
         <v>50</v>
       </c>
       <c r="AK83" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL83" t="n">
         <v>70</v>
@@ -16579,62 +16579,62 @@
         <v>1000</v>
       </c>
       <c r="AP83" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AQ83" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AR83" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="AS83" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="AT83" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AU83" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AV83" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="AW83" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="AX83" t="n">
         <v>10</v>
       </c>
       <c r="AY83" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="AZ83" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="BA83" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BB83" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BC83" t="n">
         <v>2.48</v>
       </c>
-      <c r="BB83" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BC83" t="n">
-        <v>2.4</v>
-      </c>
       <c r="BD83" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="BE83" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="BF83" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="BG83" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -16665,22 +16665,22 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="G84" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="H84" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="I84" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="J84" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="K84" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="L84" t="n">
         <v>1.37</v>
@@ -16689,7 +16689,7 @@
         <v>1.07</v>
       </c>
       <c r="N84" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="O84" t="n">
         <v>1.31</v>
@@ -16698,7 +16698,7 @@
         <v>1.73</v>
       </c>
       <c r="Q84" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="R84" t="n">
         <v>1.27</v>
@@ -16713,10 +16713,10 @@
         <v>1.01</v>
       </c>
       <c r="V84" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W84" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="X84" t="n">
         <v>1000</v>
@@ -16773,52 +16773,52 @@
         <v>1000</v>
       </c>
       <c r="AP84" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ84" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AR84" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AS84" t="n">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="AT84" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU84" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV84" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AW84" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="AX84" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY84" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ84" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA84" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BB84" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BC84" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BD84" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BE84" t="n">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="BF84" t="n">
         <v>1.01</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -16877,10 +16877,10 @@
         <v>4.2</v>
       </c>
       <c r="L85" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M85" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N85" t="n">
         <v>1.94</v>
@@ -16889,7 +16889,7 @@
         <v>1.31</v>
       </c>
       <c r="P85" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="Q85" t="n">
         <v>1.97</v>
@@ -16898,7 +16898,7 @@
         <v>1.11</v>
       </c>
       <c r="S85" t="n">
-        <v>1.02</v>
+        <v>1.98</v>
       </c>
       <c r="T85" t="n">
         <v>1.01</v>
@@ -16961,68 +16961,68 @@
         <v>1000</v>
       </c>
       <c r="AN85" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO85" t="n">
         <v>1000</v>
       </c>
       <c r="AP85" t="n">
-        <v>2.24</v>
+        <v>2.62</v>
       </c>
       <c r="AQ85" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AR85" t="n">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="AS85" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="AT85" t="n">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="AU85" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="AV85" t="n">
-        <v>2.32</v>
+        <v>2.74</v>
       </c>
       <c r="AW85" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AY85" t="n">
         <v>2.46</v>
       </c>
-      <c r="AX85" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AY85" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AZ85" t="n">
-        <v>2.32</v>
+        <v>2.74</v>
       </c>
       <c r="BA85" t="n">
-        <v>2.46</v>
+        <v>2.94</v>
       </c>
       <c r="BB85" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="BC85" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="BD85" t="n">
-        <v>2.4</v>
+        <v>2.84</v>
       </c>
       <c r="BE85" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="BF85" t="n">
-        <v>2.52</v>
+        <v>7.8</v>
       </c>
       <c r="BG85" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -17074,10 +17074,10 @@
         <v>1.01</v>
       </c>
       <c r="M86" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N86" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O86" t="n">
         <v>1.11</v>
@@ -17161,52 +17161,52 @@
         <v>1000</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR86" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS86" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT86" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU86" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV86" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW86" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX86" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY86" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ86" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA86" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB86" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC86" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD86" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE86" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF86" t="n">
         <v>1.01</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>
@@ -17410,7 +17410,589 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Jaguares de Cordoba</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G88" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I88" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J88" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K88" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" t="n">
+        <v>0</v>
+      </c>
+      <c r="X88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH88" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:37:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Boyaca Chico</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G89" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H89" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I89" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J89" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K89" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH89" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:37:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>CD Leones del Norte</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Aucas</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>3</v>
+      </c>
+      <c r="G90" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H90" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I90" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J90" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K90" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N90" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P90" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R90" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S90" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V90" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W90" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP90" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ90" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR90" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS90" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT90" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU90" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV90" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW90" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX90" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY90" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ90" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA90" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB90" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC90" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD90" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE90" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG90" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH90" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-17.xlsx
@@ -772,7 +772,7 @@
         <v>4.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -781,7 +781,7 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>1.11</v>
+        <v>3.5</v>
       </c>
       <c r="O2" t="n">
         <v>1.11</v>
@@ -811,16 +811,16 @@
         <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Y2" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z2" t="n">
         <v>36</v>
       </c>
       <c r="AA2" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB2" t="n">
         <v>23</v>
@@ -847,7 +847,7 @@
         <v>32</v>
       </c>
       <c r="AJ2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK2" t="n">
         <v>19</v>
@@ -871,10 +871,10 @@
         <v>24</v>
       </c>
       <c r="AR2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT2" t="n">
         <v>16.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G3" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="H3" t="n">
         <v>3.6</v>
@@ -1002,7 +1002,7 @@
         <v>1.34</v>
       </c>
       <c r="W3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X3" t="n">
         <v>42</v>
@@ -1059,10 +1059,10 @@
         <v>19</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR3" t="n">
         <v>7.2</v>
@@ -1080,7 +1080,7 @@
         <v>14.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX3" t="n">
         <v>15.5</v>
@@ -1092,7 +1092,7 @@
         <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB3" t="n">
         <v>20</v>
@@ -1104,7 +1104,7 @@
         <v>19</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF3" t="n">
         <v>5.8</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
         <v>16</v>
       </c>
       <c r="AR4" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS4" t="n">
         <v>36</v>
@@ -1271,44 +1271,44 @@
         <v>8.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AX4" t="n">
         <v>15</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BC4" t="n">
         <v>15</v>
       </c>
       <c r="BD4" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG4" t="n">
         <v>14</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
         <v>2.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R5" t="n">
         <v>1.49</v>
@@ -1387,7 +1387,7 @@
         <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="W5" t="n">
         <v>1.14</v>
@@ -1474,13 +1474,13 @@
         <v>5.3</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB5" t="n">
         <v>5.6</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
         <v>4.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1683,7 +1683,7 @@
         <v>14.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE6" t="n">
         <v>10</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
         <v>2.96</v>
       </c>
       <c r="X7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Y7" t="n">
         <v>30</v>
@@ -1799,7 +1799,7 @@
         <v>12</v>
       </c>
       <c r="AD7" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AQ7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV7" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU7" t="n">
+      <c r="AW7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB7" t="n">
         <v>4.7</v>
       </c>
-      <c r="AV7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BC7" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.94</v>
+        <v>2.58</v>
       </c>
       <c r="G8" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>2.36</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
         <v>1.33</v>
@@ -1945,22 +1945,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.78</v>
+        <v>3.6</v>
       </c>
       <c r="O8" t="n">
         <v>1.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -1969,10 +1969,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>2.86</v>
       </c>
       <c r="K9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,16 +2139,16 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="O9" t="n">
         <v>1.35</v>
       </c>
       <c r="P9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R9" t="n">
         <v>1.25</v>
@@ -2181,7 +2181,7 @@
         <v>90</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AC9" t="n">
         <v>11</v>
@@ -2193,7 +2193,7 @@
         <v>60</v>
       </c>
       <c r="AF9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG9" t="n">
         <v>970</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AU9" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AV9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB9" t="n">
         <v>2.36</v>
       </c>
-      <c r="AX9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BA9" t="n">
+      <c r="BC9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BD9" t="n">
         <v>2.38</v>
       </c>
-      <c r="BB9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>2.36</v>
-      </c>
       <c r="BE9" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G10" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="I10" t="n">
         <v>3.3</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2342,13 +2342,13 @@
         <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2360,7 +2360,7 @@
         <v>1.43</v>
       </c>
       <c r="W10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="G11" t="n">
         <v>1.85</v>
@@ -2518,31 +2518,31 @@
         <v>3.3</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="O11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P11" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="Q11" t="n">
         <v>1.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="S11" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -2754,10 +2754,10 @@
         <v>19.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA12" t="n">
         <v>60</v>
@@ -2769,7 +2769,7 @@
         <v>10</v>
       </c>
       <c r="AD12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE12" t="n">
         <v>40</v>
@@ -2778,10 +2778,10 @@
         <v>21</v>
       </c>
       <c r="AG12" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI12" t="n">
         <v>50</v>
@@ -2814,7 +2814,7 @@
         <v>15.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AT12" t="n">
         <v>8.6</v>
@@ -2826,7 +2826,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AX12" t="n">
         <v>12.5</v>
@@ -2838,19 +2838,19 @@
         <v>12</v>
       </c>
       <c r="BA12" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BC12" t="n">
         <v>19</v>
       </c>
       <c r="BD12" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF12" t="n">
         <v>14.5</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -2927,7 +2927,7 @@
         <v>1.69</v>
       </c>
       <c r="R13" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S13" t="n">
         <v>2.72</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
         <v>70</v>
       </c>
       <c r="AM14" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="AN14" t="n">
         <v>3.05</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -3676,10 +3676,10 @@
         <v>1.09</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K17" t="n">
         <v>5.1</v>
@@ -3691,22 +3691,22 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="O17" t="n">
         <v>1.27</v>
       </c>
       <c r="P17" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R17" t="n">
         <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -3715,7 +3715,7 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W17" t="n">
         <v>2.94</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
         <v>5.4</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
         <v>1.03</v>
@@ -4091,7 +4091,7 @@
         <v>1.47</v>
       </c>
       <c r="R19" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="S19" t="n">
         <v>2.18</v>
@@ -4118,7 +4118,7 @@
         <v>60</v>
       </c>
       <c r="AA19" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB19" t="n">
         <v>14.5</v>
@@ -4214,11 +4214,11 @@
         <v>4.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="G24" t="n">
         <v>3.1</v>
@@ -5034,7 +5034,7 @@
         <v>2.96</v>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="J24" t="n">
         <v>2.76</v>
@@ -5073,7 +5073,7 @@
         <v>1.69</v>
       </c>
       <c r="V24" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
         <v>1.47</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
         <v>2.82</v>
       </c>
       <c r="K25" t="n">
-        <v>950</v>
+        <v>7.6</v>
       </c>
       <c r="L25" t="n">
         <v>1.48</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -5434,22 +5434,22 @@
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N26" t="n">
         <v>3.45</v>
       </c>
       <c r="O26" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P26" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q26" t="n">
         <v>2.04</v>
       </c>
       <c r="R26" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S26" t="n">
         <v>3.7</v>
@@ -5509,16 +5509,16 @@
         <v>42</v>
       </c>
       <c r="AL26" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM26" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN26" t="n">
         <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AP26" t="n">
         <v>11.5</v>
@@ -5530,7 +5530,7 @@
         <v>13</v>
       </c>
       <c r="AS26" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT26" t="n">
         <v>10</v>
@@ -5554,29 +5554,29 @@
         <v>15</v>
       </c>
       <c r="BA26" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF26" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>6.6</v>
       </c>
       <c r="BG26" t="n">
         <v>16.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -6019,7 +6019,7 @@
         <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="O29" t="n">
         <v>1.25</v>
@@ -6052,7 +6052,7 @@
         <v>21</v>
       </c>
       <c r="Y29" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Z29" t="n">
         <v>29</v>
@@ -6067,7 +6067,7 @@
         <v>9</v>
       </c>
       <c r="AD29" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE29" t="n">
         <v>42</v>
@@ -6079,7 +6079,7 @@
         <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AI29" t="n">
         <v>46</v>
@@ -6106,13 +6106,13 @@
         <v>7.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR29" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS29" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT29" t="n">
         <v>10</v>
@@ -6124,7 +6124,7 @@
         <v>13.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX29" t="n">
         <v>12.5</v>
@@ -6136,10 +6136,10 @@
         <v>14</v>
       </c>
       <c r="BA29" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB29" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC29" t="n">
         <v>18</v>
@@ -6148,17 +6148,17 @@
         <v>8.4</v>
       </c>
       <c r="BE29" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF29" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG29" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6225,7 @@
         <v>1.6</v>
       </c>
       <c r="R30" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="S30" t="n">
         <v>2.3</v>
@@ -6237,10 +6237,10 @@
         <v>2.34</v>
       </c>
       <c r="V30" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W30" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X30" t="n">
         <v>27</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -6777,7 +6777,7 @@
         <v>3.4</v>
       </c>
       <c r="H33" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="I33" t="n">
         <v>2.62</v>
@@ -6789,7 +6789,7 @@
         <v>3.55</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M33" t="n">
         <v>1.08</v>
@@ -6819,7 +6819,7 @@
         <v>1.86</v>
       </c>
       <c r="V33" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W33" t="n">
         <v>1.42</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G34" t="n">
         <v>2.44</v>
@@ -6983,7 +6983,7 @@
         <v>3.85</v>
       </c>
       <c r="L34" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
         <v>1.07</v>
@@ -6992,7 +6992,7 @@
         <v>3.85</v>
       </c>
       <c r="O34" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P34" t="n">
         <v>2</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
         <v>1.32</v>
       </c>
       <c r="G35" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H35" t="n">
         <v>11</v>
@@ -7171,7 +7171,7 @@
         <v>12.5</v>
       </c>
       <c r="J35" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K35" t="n">
         <v>6.6</v>
@@ -7201,7 +7201,7 @@
         <v>2.38</v>
       </c>
       <c r="T35" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U35" t="n">
         <v>1.9</v>
@@ -7210,19 +7210,19 @@
         <v>1.08</v>
       </c>
       <c r="W35" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="X35" t="n">
         <v>27</v>
       </c>
       <c r="Y35" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="Z35" t="n">
         <v>120</v>
       </c>
       <c r="AA35" t="n">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="AB35" t="n">
         <v>10</v>
@@ -7231,13 +7231,13 @@
         <v>15.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AE35" t="n">
         <v>180</v>
       </c>
       <c r="AF35" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG35" t="n">
         <v>10.5</v>
@@ -7273,10 +7273,10 @@
         <v>36</v>
       </c>
       <c r="AR35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS35" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT35" t="n">
         <v>8.6</v>
@@ -7288,7 +7288,7 @@
         <v>34</v>
       </c>
       <c r="AW35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX35" t="n">
         <v>7.4</v>
@@ -7300,7 +7300,7 @@
         <v>24</v>
       </c>
       <c r="BA35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB35" t="n">
         <v>9.4</v>
@@ -7309,20 +7309,20 @@
         <v>12</v>
       </c>
       <c r="BD35" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="BE35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF35" t="n">
         <v>4.1</v>
       </c>
       <c r="BG35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
         <v>3.05</v>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="H36" t="n">
         <v>2.2</v>
@@ -7404,7 +7404,7 @@
         <v>1.56</v>
       </c>
       <c r="W36" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="G37" t="n">
         <v>4.2</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
         <v>3.65</v>
       </c>
       <c r="G38" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H38" t="n">
         <v>1.88</v>
@@ -7765,7 +7765,7 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="O38" t="n">
         <v>1.37</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
         <v>1.53</v>
       </c>
       <c r="W41" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G44" t="n">
         <v>3.5</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -9123,22 +9123,22 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="O45" t="n">
         <v>1.32</v>
       </c>
       <c r="P45" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="R45" t="n">
         <v>1.18</v>
       </c>
       <c r="S45" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="T45" t="n">
         <v>1.01</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -9338,7 +9338,7 @@
         <v>1.91</v>
       </c>
       <c r="U46" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="V46" t="n">
         <v>1.5</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9693,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="K48" t="n">
         <v>6.6</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
         <v>2.28</v>
       </c>
       <c r="G50" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="H50" t="n">
         <v>3</v>
@@ -10093,7 +10093,7 @@
         <v>1.01</v>
       </c>
       <c r="N50" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="O50" t="n">
         <v>1.29</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -10263,10 +10263,10 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G51" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H51" t="n">
         <v>4.8</v>
@@ -10287,19 +10287,19 @@
         <v>1.01</v>
       </c>
       <c r="N51" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="O51" t="n">
         <v>1.26</v>
       </c>
       <c r="P51" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="n">
         <v>1.9</v>
       </c>
       <c r="R51" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S51" t="n">
         <v>2.84</v>
@@ -10314,13 +10314,13 @@
         <v>1.25</v>
       </c>
       <c r="W51" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X51" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y51" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Z51" t="n">
         <v>55</v>
@@ -10329,7 +10329,7 @@
         <v>1000</v>
       </c>
       <c r="AB51" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC51" t="n">
         <v>13</v>
@@ -10371,62 +10371,62 @@
         <v>1000</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AQ51" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR51" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="AS51" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AU51" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AV51" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="AW51" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BD51" t="n">
         <v>2.58</v>
       </c>
-      <c r="AX51" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BD51" t="n">
-        <v>2.52</v>
-      </c>
       <c r="BE51" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="BF51" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG51" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -10493,16 +10493,16 @@
         <v>1.83</v>
       </c>
       <c r="R52" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S52" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="T52" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="U52" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V52" t="n">
         <v>1.23</v>
@@ -10547,7 +10547,7 @@
         <v>80</v>
       </c>
       <c r="AJ52" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK52" t="n">
         <v>25</v>
@@ -10607,7 +10607,7 @@
         <v>12.5</v>
       </c>
       <c r="BD52" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BE52" t="n">
         <v>2.72</v>
@@ -10616,11 +10616,11 @@
         <v>7.8</v>
       </c>
       <c r="BG52" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -11657,10 +11657,10 @@
         <v>1.44</v>
       </c>
       <c r="R58" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="S58" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="T58" t="n">
         <v>1.54</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -11821,7 +11821,7 @@
         <v>1.96</v>
       </c>
       <c r="H59" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I59" t="n">
         <v>4.4</v>
@@ -11881,7 +11881,7 @@
         <v>95</v>
       </c>
       <c r="AB59" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AC59" t="n">
         <v>19</v>
@@ -11896,7 +11896,7 @@
         <v>28</v>
       </c>
       <c r="AG59" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH59" t="n">
         <v>21</v>
@@ -11923,28 +11923,28 @@
         <v>1000</v>
       </c>
       <c r="AP59" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="AQ59" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AR59" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AS59" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="AT59" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AU59" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AV59" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AW59" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AX59" t="n">
         <v>2.38</v>
@@ -11956,10 +11956,10 @@
         <v>10</v>
       </c>
       <c r="BA59" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BB59" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BC59" t="n">
         <v>11</v>
@@ -11968,17 +11968,17 @@
         <v>15</v>
       </c>
       <c r="BE59" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BF59" t="n">
         <v>3.95</v>
       </c>
       <c r="BG59" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -12687,7 +12687,7 @@
         <v>40</v>
       </c>
       <c r="AL63" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM63" t="n">
         <v>90</v>
@@ -12702,7 +12702,7 @@
         <v>2.26</v>
       </c>
       <c r="AQ63" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AR63" t="n">
         <v>2.24</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -12788,10 +12788,10 @@
         <v>1.71</v>
       </c>
       <c r="G64" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H64" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I64" t="n">
         <v>5.1</v>
@@ -12818,7 +12818,7 @@
         <v>2.58</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R64" t="n">
         <v>1.64</v>
@@ -12827,128 +12827,128 @@
         <v>2.32</v>
       </c>
       <c r="T64" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="U64" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V64" t="n">
         <v>1.25</v>
       </c>
       <c r="W64" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X64" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Y64" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Z64" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AA64" t="n">
         <v>1000</v>
       </c>
       <c r="AB64" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AC64" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AD64" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AE64" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AF64" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AG64" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AH64" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AI64" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ64" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AK64" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AL64" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AM64" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AN64" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO64" t="n">
         <v>1000</v>
       </c>
       <c r="AP64" t="n">
-        <v>3.85</v>
+        <v>2.66</v>
       </c>
       <c r="AQ64" t="n">
-        <v>3.85</v>
+        <v>2.66</v>
       </c>
       <c r="AR64" t="n">
-        <v>4.1</v>
+        <v>2.74</v>
       </c>
       <c r="AS64" t="n">
-        <v>4.4</v>
+        <v>2.88</v>
       </c>
       <c r="AT64" t="n">
-        <v>9.800000000000001</v>
+        <v>2.48</v>
       </c>
       <c r="AU64" t="n">
-        <v>3.3</v>
+        <v>2.42</v>
       </c>
       <c r="AV64" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="AW64" t="n">
-        <v>36</v>
+        <v>2.78</v>
       </c>
       <c r="AX64" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY64" t="n">
-        <v>8.199999999999999</v>
+        <v>2.42</v>
       </c>
       <c r="AZ64" t="n">
-        <v>3.6</v>
+        <v>2.56</v>
       </c>
       <c r="BA64" t="n">
-        <v>30</v>
+        <v>2.76</v>
       </c>
       <c r="BB64" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="BC64" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD64" t="n">
         <v>18.5</v>
       </c>
       <c r="BE64" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="BF64" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BG64" t="n">
-        <v>4.4</v>
+        <v>2.86</v>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -13376,7 +13376,7 @@
         <v>2.22</v>
       </c>
       <c r="I67" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>3.85</v>
@@ -13409,13 +13409,13 @@
         <v>2.44</v>
       </c>
       <c r="T67" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U67" t="n">
         <v>2.58</v>
       </c>
       <c r="V67" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W67" t="n">
         <v>1.43</v>
@@ -13520,7 +13520,7 @@
         <v>9.4</v>
       </c>
       <c r="BE67" t="n">
-        <v>42</v>
+        <v>10.5</v>
       </c>
       <c r="BF67" t="n">
         <v>15.5</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -13561,16 +13561,16 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="G68" t="n">
         <v>4.1</v>
       </c>
       <c r="H68" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I68" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="J68" t="n">
         <v>3.15</v>
@@ -13594,13 +13594,13 @@
         <v>1.72</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R68" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="S68" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="T68" t="n">
         <v>1.87</v>
@@ -13609,7 +13609,7 @@
         <v>1.7</v>
       </c>
       <c r="V68" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W68" t="n">
         <v>1.32</v>
@@ -13669,7 +13669,7 @@
         <v>1000</v>
       </c>
       <c r="AP68" t="n">
-        <v>9.4</v>
+        <v>2.64</v>
       </c>
       <c r="AQ68" t="n">
         <v>7.2</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="G69" t="n">
         <v>1.79</v>
@@ -13911,14 +13911,14 @@
         <v>7.6</v>
       </c>
       <c r="BF69" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG69" t="n">
         <v>7.4</v>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -13982,7 +13982,7 @@
         <v>1.24</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R70" t="n">
         <v>1.18</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
         <v>7.4</v>
       </c>
       <c r="H73" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="I73" t="n">
         <v>1.99</v>
@@ -14546,7 +14546,7 @@
         <v>1.09</v>
       </c>
       <c r="K73" t="n">
-        <v>950</v>
+        <v>6.4</v>
       </c>
       <c r="L73" t="n">
         <v>1.01</v>
@@ -14582,7 +14582,7 @@
         <v>2</v>
       </c>
       <c r="W73" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X73" t="n">
         <v>1000</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -14761,7 +14761,7 @@
         <v>1.61</v>
       </c>
       <c r="R74" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S74" t="n">
         <v>2.58</v>
@@ -14797,7 +14797,7 @@
         <v>18</v>
       </c>
       <c r="AD74" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AE74" t="n">
         <v>360</v>
@@ -14812,7 +14812,7 @@
         <v>46</v>
       </c>
       <c r="AI74" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ74" t="n">
         <v>8.800000000000001</v>
@@ -14842,7 +14842,7 @@
         <v>44</v>
       </c>
       <c r="AS74" t="n">
-        <v>15.5</v>
+        <v>60</v>
       </c>
       <c r="AT74" t="n">
         <v>8.199999999999999</v>
@@ -14854,7 +14854,7 @@
         <v>46</v>
       </c>
       <c r="AW74" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="AX74" t="n">
         <v>6.8</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -15116,7 +15116,7 @@
         <v>1.79</v>
       </c>
       <c r="G76" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="H76" t="n">
         <v>4.6</v>
@@ -15137,22 +15137,22 @@
         <v>1.05</v>
       </c>
       <c r="N76" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O76" t="n">
         <v>1.3</v>
       </c>
       <c r="P76" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="R76" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S76" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T76" t="n">
         <v>1.8</v>
@@ -15164,7 +15164,7 @@
         <v>1.23</v>
       </c>
       <c r="W76" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X76" t="n">
         <v>18.5</v>
@@ -15179,7 +15179,7 @@
         <v>1000</v>
       </c>
       <c r="AB76" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC76" t="n">
         <v>10.5</v>
@@ -15242,7 +15242,7 @@
         <v>13</v>
       </c>
       <c r="AW76" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX76" t="n">
         <v>8.800000000000001</v>
@@ -15254,7 +15254,7 @@
         <v>13.5</v>
       </c>
       <c r="BA76" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB76" t="n">
         <v>15.5</v>
@@ -15266,17 +15266,17 @@
         <v>4.2</v>
       </c>
       <c r="BE76" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF76" t="n">
         <v>9.4</v>
       </c>
       <c r="BG76" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -15331,7 +15331,7 @@
         <v>1.09</v>
       </c>
       <c r="N77" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O77" t="n">
         <v>1.41</v>
@@ -15346,7 +15346,7 @@
         <v>1.25</v>
       </c>
       <c r="S77" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T77" t="n">
         <v>1.89</v>
@@ -15370,10 +15370,10 @@
         <v>29</v>
       </c>
       <c r="AA77" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB77" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AC77" t="n">
         <v>8.4</v>
@@ -15382,22 +15382,22 @@
         <v>18</v>
       </c>
       <c r="AE77" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF77" t="n">
         <v>16</v>
       </c>
       <c r="AG77" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH77" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI77" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ77" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK77" t="n">
         <v>34</v>
@@ -15409,7 +15409,7 @@
         <v>1000</v>
       </c>
       <c r="AN77" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AO77" t="n">
         <v>1000</v>
@@ -15421,7 +15421,7 @@
         <v>9</v>
       </c>
       <c r="AR77" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS77" t="n">
         <v>5.6</v>
@@ -15430,13 +15430,13 @@
         <v>7.2</v>
       </c>
       <c r="AU77" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV77" t="n">
         <v>12</v>
       </c>
       <c r="AW77" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AX77" t="n">
         <v>10.5</v>
@@ -15448,16 +15448,16 @@
         <v>15</v>
       </c>
       <c r="BA77" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BB77" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BC77" t="n">
         <v>21</v>
       </c>
       <c r="BD77" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BE77" t="n">
         <v>5.8</v>
@@ -15466,11 +15466,11 @@
         <v>19</v>
       </c>
       <c r="BG77" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -15698,7 +15698,7 @@
         <v>1.92</v>
       </c>
       <c r="G79" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="H79" t="n">
         <v>3.4</v>
@@ -15746,7 +15746,7 @@
         <v>1.28</v>
       </c>
       <c r="W79" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="X79" t="n">
         <v>1000</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -15889,22 +15889,22 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G80" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H80" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="I80" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J80" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="K80" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="L80" t="n">
         <v>1.35</v>
@@ -15913,19 +15913,19 @@
         <v>1.01</v>
       </c>
       <c r="N80" t="n">
-        <v>1.63</v>
+        <v>3.2</v>
       </c>
       <c r="O80" t="n">
         <v>1.38</v>
       </c>
       <c r="P80" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R80" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S80" t="n">
         <v>3.5</v>
@@ -15937,7 +15937,7 @@
         <v>1.01</v>
       </c>
       <c r="V80" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W80" t="n">
         <v>1.5</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -16197,7 +16197,7 @@
         <v>21</v>
       </c>
       <c r="AR81" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="AS81" t="n">
         <v>11.5</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -16480,10 +16480,10 @@
         <v>3.2</v>
       </c>
       <c r="I83" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="J83" t="n">
-        <v>3.15</v>
+        <v>2.54</v>
       </c>
       <c r="K83" t="n">
         <v>3.6</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -16668,13 +16668,13 @@
         <v>1.57</v>
       </c>
       <c r="G84" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="H84" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I84" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="J84" t="n">
         <v>3.55</v>
@@ -16713,10 +16713,10 @@
         <v>1.01</v>
       </c>
       <c r="V84" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W84" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="X84" t="n">
         <v>1000</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -17471,10 +17471,10 @@
         <v>1.39</v>
       </c>
       <c r="P88" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="R88" t="n">
         <v>1.21</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -17653,152 +17653,152 @@
         <v>3.4</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P89" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q89" t="n">
         <v>2.54</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI89" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK89" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL89" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM89" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN89" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO89" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP89" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AR89" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AS89" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AT89" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AU89" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AV89" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AW89" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AX89" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AY89" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AZ89" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BA89" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BB89" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC89" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BD89" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BE89" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BF89" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG89" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -17832,7 +17832,7 @@
         <v>3</v>
       </c>
       <c r="G90" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="H90" t="n">
         <v>2.54</v>
@@ -17880,7 +17880,7 @@
         <v>1.52</v>
       </c>
       <c r="W90" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X90" t="n">
         <v>1000</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -18050,7 +18050,7 @@
         <v>1.46</v>
       </c>
       <c r="O91" t="n">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="P91" t="n">
         <v>1.46</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
@@ -18217,22 +18217,22 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G92" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H92" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I92" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="J92" t="n">
-        <v>1.82</v>
+        <v>3.6</v>
       </c>
       <c r="K92" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L92" t="n">
         <v>1.01</v>
@@ -18244,7 +18244,7 @@
         <v>1.64</v>
       </c>
       <c r="O92" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P92" t="n">
         <v>1.64</v>
@@ -18265,10 +18265,10 @@
         <v>1.01</v>
       </c>
       <c r="V92" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W92" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="X92" t="n">
         <v>1000</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-15 21:51:30</t>
+          <t>2026-04-16 00:04:54</t>
         </is>
       </c>
     </row>
